--- a/examples/TAURI_REWRITE/EXCEL/ReferenceTable.xlsx
+++ b/examples/TAURI_REWRITE/EXCEL/ReferenceTable.xlsx
@@ -9,13 +9,14 @@
     <sheet sheetId="3" name="CycleA" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="CycleB" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="_DropDown" state="veryHidden" r:id="rId8"/>
+    <sheet sheetId="6" name="_DataManager" state="veryHidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -51,6 +52,12 @@
   </si>
   <si>
     <t>FixtureState_ACTIVE</t>
+  </si>
+  <si>
+    <t>DataManager.ExcelMetadata</t>
+  </si>
+  <si>
+    <t>{"magic":"DataManager.ExcelMetadata","version":1,"sourceFile":"ReferenceTable.proto","fingerprint":"dm1-cb3f1990","tables":[{"messageName":"MiddleTarget","memoColumns":[]},{"messageName":"RootTarget","memoColumns":[]},{"messageName":"CycleA","memoColumns":[]},{"messageName":"CycleB","memoColumns":[]}]}</t>
   </si>
 </sst>
 </file>
@@ -608,4 +615,28 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>